--- a/example/template_e.xlsx
+++ b/example/template_e.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аркуш1" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,11 +20,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Aptos Narrow"/>
       <charset val="204"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <charset val="204"/>
+      <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -50,11 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -62,6 +69,8 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
@@ -460,10 +469,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="5" t="inlineStr">
+    <row r="1" ht="70" customHeight="1" s="6">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>{{field_4}}</t>
         </is>
@@ -478,63 +487,66 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Молоко</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>{{field_5}}</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Хлеб</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>{{field_6}}</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Картошка</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>{{field_7}}</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Картошка</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Макароны</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>{{field_8}}</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Макароны</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>{{field_9}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{{field_10}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+    <row r="8"/>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Итого</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
-      <c r="B10" s="1" t="n"/>
+      <c r="B10" s="1">
+        <f>SUM(B4:B7)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -549,41 +561,41 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <sheetData>
     <row r="1"/>
     <row r="2"/>
     <row r="3"/>
     <row r="4"/>
-    <row r="5">
-      <c r="B5" s="6" t="inlineStr">
+    <row r="5" ht="70" customHeight="1" s="6">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>{{field_4}}</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>{{field_2}}</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>{{field_5}}</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>{{field_6}}</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>{{field_7}}</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>{{field_8}}</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>{{field_9}}</t>
         </is>
       </c>
     </row>
@@ -591,7 +603,7 @@
     <row r="7"/>
     <row r="8"/>
     <row r="9">
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>{{{field_2}}}</t>
         </is>
@@ -609,7 +621,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <sheetData>
     <row r="1"/>
   </sheetData>
@@ -624,7 +636,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <sheetData>
     <row r="1"/>
   </sheetData>
@@ -639,7 +651,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <sheetData>
     <row r="1"/>
   </sheetData>
